--- a/tests/fixtures/22_weekly_timesheet/pattern.xlsx
+++ b/tests/fixtures/22_weekly_timesheet/pattern.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:L69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,7 +441,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>l_emp</t>
+          <t>timesheet_label</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -451,7 +451,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Employee:</t>
+          <t>TIME SHEET</t>
         </is>
       </c>
     </row>
@@ -463,7 +463,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>l_week</t>
+          <t>address_label</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -473,7 +473,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Week starting:</t>
+          <t>222 2nd Ave</t>
         </is>
       </c>
     </row>
@@ -485,7 +485,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>c_day</t>
+          <t>employee_name_label</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -495,7 +495,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Employee name:</t>
         </is>
       </c>
     </row>
@@ -507,7 +507,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>c_in</t>
+          <t>shir_rosenstein_label</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -517,7 +517,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Time in</t>
+          <t>Shir Rosenstein</t>
         </is>
       </c>
     </row>
@@ -529,7 +529,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>c_out</t>
+          <t>col_day_of_week</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -539,7 +539,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Time out</t>
+          <t>Day of week</t>
         </is>
       </c>
     </row>
@@ -551,7 +551,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>c_break</t>
+          <t>col_time_in</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -561,7 +561,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Break</t>
+          <t>Time in</t>
         </is>
       </c>
     </row>
@@ -573,7 +573,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>c_total</t>
+          <t>col_breaks</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -583,19 +583,19 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Breaks\n(minutes)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>var:</t>
+          <t>lbl:</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>sheet.employee</t>
+          <t>col_time_out</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -605,37 +605,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>.+</t>
+          <t>Time out</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>var:</t>
+          <t>lbl:</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>sheet.week_starting</t>
+          <t>col_total</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Total\n[h]:mm</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>var:</t>
+          <t>lbl:</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>day.name</t>
+          <t>col_regular</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -645,77 +649,85 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>.+</t>
+          <t>Regular\n[h]:mm</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>var:</t>
+          <t>lbl:</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>day.time_in</t>
+          <t>col_overtime</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Overtime\n[h]:mm</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>var:</t>
+          <t>lbl:</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>day.time_out</t>
+          <t>col_sick</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Sick\n[h]:mm</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>var:</t>
+          <t>lbl:</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>day.break_min</t>
+          <t>col_holiday</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>\d+</t>
+          <t>Holiday\n[h]:mm</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>var:</t>
+          <t>lbl:</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>day.total</t>
+          <t>col_vacation</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -725,114 +737,1188 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>.*</t>
+          <t>Vacation\n[h]:mm</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>START:</t>
+          <t>lbl:</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>col_regular_pay</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Regular</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>cell:C4</t>
+          <t>lbl:</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>sheet.employee</t>
+          <t>col_overtime_pay</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Overtime</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>cell:C5</t>
+          <t>lbl:</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>sheet.week_starting</t>
+          <t>col_sick_pay</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Sick</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>table:*</t>
+          <t>lbl:</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>col_holiday_pay</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Holiday</t>
         </is>
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>lbl:</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>HEADER:1</t>
+          <t>col_vacation_pay</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>c_day</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>c_in</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>c_out</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>c_break</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>c_total</t>
+          <t>Vacation</t>
         </is>
       </c>
     </row>
     <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>lbl:</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DATA:*</t>
+          <t>manager_signature_label</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>day.name</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>day.time_in</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>day.time_out</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>day.break_min</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>day.total</t>
+          <t>Manager Signature</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
+        <is>
+          <t>lbl:</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>grand_total_label</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Grand total pay:</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>var:</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>company.name</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>.*</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>var:</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>employee.name</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>.*</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>var:</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>employee.date</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>var:</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>week1.day_of_week</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>datetime</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>var:</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>week1.time_in</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>.*</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>var:</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>week1.breaks</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>\d+</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>var:</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>week1.time_out</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>.*</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>var:</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>week1.total</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>.*</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>var:</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>week1.regular</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>.*</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>var:</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>week1.overtime</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>.*</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>var:</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>week1.sick</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>.*</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>var:</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>week1.holiday</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>.*</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>var:</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>week1.vacation</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>.*</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>var:</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>week2.day_of_week</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>datetime</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>var:</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>week2.total</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>.*</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>var:</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>week2.regular</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>.*</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>var:</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>week2.overtime</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>.*</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>var:</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>week2.sick</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>.*</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>var:</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>week2.holiday</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>.*</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>var:</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>week2.vacation</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>.*</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>var:</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>pay.regular</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>\d+(\.\d{1,2})?</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>var:</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>pay.overtime</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>\d+(\.\d{1,2})?</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>var:</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>pay.sick</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>\d+(\.\d{1,2})?</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>var:</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>pay.holiday</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>\d+(\.\d{1,2})?</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>var:</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>pay.vacation</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>\d+(\.\d{1,2})?</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>var:</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>manager.signature</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>.*</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>var:</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>sheet.grand_total</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>\d+(\.\d{1,2})?</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>START:</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>cell:next</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>timesheet_label</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>cell:next</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>company.name</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>table:*</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>HEADER:1</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>address_label</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>employee_name_label</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>shir_rosenstein_label</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>DATA:3</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>IGNORE</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>employee.name</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>employee.date</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>table:*</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>HEADER:1</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>col_day_of_week</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>col_time_in</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>col_breaks</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>col_time_out</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>col_total</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>col_regular</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>col_overtime</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>col_sick</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>col_holiday</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>col_vacation</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>DATA:8</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>week1.day_of_week</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>week1.time_in</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>week1.breaks</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>week1.time_out</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>week1.total</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>week1.regular</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>week1.overtime</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>week1.sick</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>week1.holiday</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>week1.vacation</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>table:*</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>HEADER:1</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>col_day_of_week</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>col_time_in</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>col_breaks</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>col_time_out</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>col_total</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>col_regular</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>col_overtime</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>col_sick</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>col_holiday</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>col_vacation</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>DATA:8</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>week2.day_of_week</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>IGNORE</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>IGNORE</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>IGNORE</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>week2.total</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>week2.regular</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>week2.overtime</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>week2.sick</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>week2.holiday</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>week2.vacation</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>table:*</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>HEADER:1</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>col_regular_pay</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>col_overtime_pay</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>col_sick_pay</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>col_holiday_pay</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>col_vacation_pay</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>DATA:2</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>pay.regular</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>pay.overtime</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>pay.sick</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>pay.holiday</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>pay.vacation</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>cell:next</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>manager_signature_label</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>cell:next</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>manager.signature</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>cell:next</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>grand_total_label</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>cell:next</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>sheet.grand_total</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
         <is>
           <t>END:</t>
         </is>

--- a/tests/fixtures/22_weekly_timesheet/pattern.xlsx
+++ b/tests/fixtures/22_weekly_timesheet/pattern.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L69"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,7 +441,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>timesheet_label</t>
+          <t>col_day</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -451,7 +451,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>TIME SHEET</t>
+          <t>Day of week</t>
         </is>
       </c>
     </row>
@@ -463,7 +463,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>address_label</t>
+          <t>col_time_in</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -473,7 +473,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>222 2nd Ave</t>
+          <t>Time in</t>
         </is>
       </c>
     </row>
@@ -485,7 +485,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>employee_name_label</t>
+          <t>col_breaks</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -495,7 +495,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Employee name:</t>
+          <t>Breaks\n\(minutes\)</t>
         </is>
       </c>
     </row>
@@ -507,7 +507,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>shir_rosenstein_label</t>
+          <t>col_time_out</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -517,19 +517,19 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Shir Rosenstein</t>
+          <t>Time out</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>lbl:</t>
+          <t>var:</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>col_day_of_week</t>
+          <t>company.name</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -539,19 +539,19 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Day of week</t>
+          <t>.*</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>lbl:</t>
+          <t>var:</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>col_time_in</t>
+          <t>employee.name</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -561,19 +561,19 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Time in</t>
+          <t>.*</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>lbl:</t>
+          <t>var:</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>col_breaks</t>
+          <t>employee.manager</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -583,315 +583,299 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Breaks\n(minutes)</t>
+          <t>.*</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>lbl:</t>
+          <t>var:</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>col_time_out</t>
+          <t>employee.week_starting</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Time out</t>
-        </is>
-      </c>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>lbl:</t>
+          <t>var:</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>col_total</t>
+          <t>week.day</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Total\n[h]:mm</t>
-        </is>
-      </c>
+          <t>datetime</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>lbl:</t>
+          <t>var:</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>col_regular</t>
+          <t>week.time_in</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Regular\n[h]:mm</t>
-        </is>
-      </c>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>lbl:</t>
+          <t>var:</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>col_overtime</t>
+          <t>week.breaks</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Overtime\n[h]:mm</t>
+          <t>\d+</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>lbl:</t>
+          <t>var:</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>col_sick</t>
+          <t>week.time_out</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Sick\n[h]:mm</t>
-        </is>
-      </c>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>lbl:</t>
+          <t>var:</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>col_holiday</t>
+          <t>rate.regular</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Holiday\n[h]:mm</t>
+          <t>.*</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>lbl:</t>
+          <t>var:</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>col_vacation</t>
+          <t>rate.overtime</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Vacation\n[h]:mm</t>
+          <t>.*</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>lbl:</t>
+          <t>var:</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>col_regular_pay</t>
+          <t>rate.sick</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>.*</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>lbl:</t>
+          <t>var:</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>col_overtime_pay</t>
+          <t>rate.holiday</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Overtime</t>
+          <t>.*</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>lbl:</t>
+          <t>var:</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>col_sick_pay</t>
+          <t>rate.vacation</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Sick</t>
+          <t>.*</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>lbl:</t>
+          <t>var:</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>col_holiday_pay</t>
+          <t>pay.regular</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Holiday</t>
+          <t>.*</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>lbl:</t>
+          <t>var:</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>col_vacation_pay</t>
+          <t>pay.overtime</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Vacation</t>
+          <t>.*</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>lbl:</t>
+          <t>var:</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>manager_signature_label</t>
+          <t>pay.sick</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Manager Signature</t>
+          <t>.*</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>lbl:</t>
+          <t>var:</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>grand_total_label</t>
+          <t>pay.holiday</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Grand total pay:</t>
+          <t>.*</t>
         </is>
       </c>
     </row>
@@ -903,12 +887,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>company.name</t>
+          <t>pay.vacation</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -925,12 +909,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>employee.name</t>
+          <t>pay.grand_total</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -942,983 +926,253 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>var:</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>employee.date</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>date</t>
+          <t>START:</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>var:</t>
+          <t>cell:G2</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>week1.day_of_week</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>datetime</t>
+          <t>company.name</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>var:</t>
+          <t>cell:I4</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>week1.time_in</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>.*</t>
+          <t>employee.name</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>var:</t>
+          <t>cell:I5</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>week1.breaks</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>\d+</t>
+          <t>employee.manager</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>var:</t>
+          <t>cell:I6</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>week1.time_out</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>.*</t>
+          <t>employee.week_starting</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>var:</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>week1.total</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>.*</t>
+          <t>table:*</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>var:</t>
-        </is>
-      </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>week1.regular</t>
+          <t>HEADER:1</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>col_day</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>.*</t>
+          <t>col_time_in</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>col_breaks</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>col_time_out</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>var:</t>
-        </is>
-      </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>week1.overtime</t>
+          <t>DATA:8</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>week.day</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>.*</t>
+          <t>week.time_in</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>week.breaks</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>week.time_out</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>var:</t>
+          <t>cell:H30</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>week1.sick</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>.*</t>
+          <t>rate.regular</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>var:</t>
+          <t>cell:I30</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>week1.holiday</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>.*</t>
+          <t>rate.overtime</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>var:</t>
+          <t>cell:J30</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>week1.vacation</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>.*</t>
+          <t>rate.sick</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>var:</t>
+          <t>cell:K30</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>week2.day_of_week</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>datetime</t>
+          <t>rate.holiday</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>var:</t>
+          <t>cell:L30</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>week2.total</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>.*</t>
+          <t>rate.vacation</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>var:</t>
+          <t>cell:H31</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>week2.regular</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>.*</t>
+          <t>pay.regular</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>var:</t>
+          <t>cell:I31</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>week2.overtime</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>.*</t>
+          <t>pay.overtime</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>var:</t>
+          <t>cell:J31</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>week2.sick</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>.*</t>
+          <t>pay.sick</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>var:</t>
+          <t>cell:K31</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>week2.holiday</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>.*</t>
+          <t>pay.holiday</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>var:</t>
+          <t>cell:L31</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>week2.vacation</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>.*</t>
+          <t>pay.vacation</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>var:</t>
+          <t>cell:K33</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>pay.regular</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>\d+(\.\d{1,2})?</t>
+          <t>pay.grand_total</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
-        <is>
-          <t>var:</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>pay.overtime</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>\d+(\.\d{1,2})?</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>var:</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>pay.sick</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>\d+(\.\d{1,2})?</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>var:</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>pay.holiday</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>\d+(\.\d{1,2})?</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>var:</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>pay.vacation</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>\d+(\.\d{1,2})?</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>var:</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>manager.signature</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>.*</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>var:</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>sheet.grand_total</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>\d+(\.\d{1,2})?</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>START:</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>cell:next</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>timesheet_label</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>cell:next</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>company.name</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>table:*</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>HEADER:1</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>address_label</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>employee_name_label</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>shir_rosenstein_label</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>DATA:3</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>IGNORE</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>employee.name</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>employee.date</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>table:*</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>HEADER:1</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>col_day_of_week</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>col_time_in</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>col_breaks</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>col_time_out</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>col_total</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>col_regular</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>col_overtime</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>col_sick</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>col_holiday</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>col_vacation</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>DATA:8</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>week1.day_of_week</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>week1.time_in</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>week1.breaks</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>week1.time_out</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>week1.total</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>week1.regular</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>week1.overtime</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>week1.sick</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>week1.holiday</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>week1.vacation</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>table:*</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>HEADER:1</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>col_day_of_week</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>col_time_in</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>col_breaks</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>col_time_out</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>col_total</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>col_regular</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>col_overtime</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>col_sick</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>col_holiday</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>col_vacation</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>DATA:8</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>week2.day_of_week</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>IGNORE</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>IGNORE</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>IGNORE</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>week2.total</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>week2.regular</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>week2.overtime</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>week2.sick</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>week2.holiday</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>week2.vacation</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>table:*</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>HEADER:1</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>col_regular_pay</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>col_overtime_pay</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>col_sick_pay</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>col_holiday_pay</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>col_vacation_pay</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>DATA:2</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>pay.regular</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>pay.overtime</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>pay.sick</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>pay.holiday</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>pay.vacation</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>cell:next</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>manager_signature_label</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>cell:next</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>manager.signature</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>cell:next</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>grand_total_label</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>cell:next</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>sheet.grand_total</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
         <is>
           <t>END:</t>
         </is>

--- a/tests/fixtures/22_weekly_timesheet/pattern.xlsx
+++ b/tests/fixtures/22_weekly_timesheet/pattern.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,7 +441,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>l_emp</t>
+          <t>col_day</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -451,7 +451,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Employee:</t>
+          <t>Day of week</t>
         </is>
       </c>
     </row>
@@ -463,7 +463,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>l_week</t>
+          <t>col_time_in</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -473,7 +473,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Week starting:</t>
+          <t>Time in</t>
         </is>
       </c>
     </row>
@@ -485,7 +485,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>c_day</t>
+          <t>col_breaks</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -495,7 +495,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Breaks\n\(minutes\)</t>
         </is>
       </c>
     </row>
@@ -507,7 +507,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>c_in</t>
+          <t>col_time_out</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -517,19 +517,19 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Time in</t>
+          <t>Time out</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>lbl:</t>
+          <t>var:</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>c_out</t>
+          <t>company.name</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -539,19 +539,19 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Time out</t>
+          <t>.*</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>lbl:</t>
+          <t>var:</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>c_break</t>
+          <t>employee.name</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -561,19 +561,19 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Break</t>
+          <t>.*</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>lbl:</t>
+          <t>var:</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>c_total</t>
+          <t>employee.manager</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -583,7 +583,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>.*</t>
         </is>
       </c>
     </row>
@@ -595,19 +595,15 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>sheet.employee</t>
+          <t>employee.week_starting</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>.+</t>
-        </is>
-      </c>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -617,12 +613,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>sheet.week_starting</t>
+          <t>week.day</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>datetime</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -635,19 +631,15 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>day.name</t>
+          <t>week.time_in</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>.+</t>
-        </is>
-      </c>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -657,15 +649,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>day.time_in</t>
+          <t>week.breaks</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>\d+</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -675,7 +671,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>day.time_out</t>
+          <t>week.time_out</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -693,17 +689,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>day.break_min</t>
+          <t>rate.regular</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>\d+</t>
+          <t>.*</t>
         </is>
       </c>
     </row>
@@ -715,12 +711,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>day.total</t>
+          <t>rate.overtime</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -732,107 +728,451 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>START:</t>
+          <t>var:</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>rate.sick</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>.*</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>cell:C4</t>
+          <t>var:</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>sheet.employee</t>
+          <t>rate.holiday</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>.*</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>cell:C5</t>
+          <t>var:</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>sheet.week_starting</t>
+          <t>rate.vacation</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>.*</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>table:*</t>
+          <t>var:</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>pay.regular</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>.*</t>
         </is>
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>var:</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>HEADER:1</t>
+          <t>pay.overtime</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>c_day</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>c_in</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>c_out</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>c_break</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>c_total</t>
+          <t>.*</t>
         </is>
       </c>
     </row>
     <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>var:</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DATA:*</t>
+          <t>pay.sick</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>day.name</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>day.time_in</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>day.time_out</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>day.break_min</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>day.total</t>
+          <t>.*</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
+        <is>
+          <t>var:</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>pay.holiday</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>.*</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>var:</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>pay.vacation</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>.*</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>var:</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>pay.grand_total</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>.*</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>START:</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>cell:G2</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>company.name</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>cell:I4</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>employee.name</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>cell:I5</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>employee.manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>cell:I6</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>employee.week_starting</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>table:*</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>HEADER:1</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>col_day</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>col_time_in</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>col_breaks</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>col_time_out</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>DATA:8</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>week.day</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>week.time_in</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>week.breaks</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>week.time_out</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>cell:H30</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>rate.regular</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>cell:I30</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>rate.overtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>cell:J30</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>rate.sick</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>cell:K30</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>rate.holiday</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>cell:L30</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>rate.vacation</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>cell:H31</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>pay.regular</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>cell:I31</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>pay.overtime</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>cell:J31</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>pay.sick</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>cell:K31</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>pay.holiday</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>cell:L31</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>pay.vacation</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>cell:K33</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>pay.grand_total</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
         <is>
           <t>END:</t>
         </is>
